--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:29:22+00:00</t>
+    <t>2025-02-13T14:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:40:19+00:00</t>
+    <t>2025-02-13T14:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:46:33+00:00</t>
+    <t>2025-02-13T14:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:59:23+00:00</t>
+    <t>2025-02-14T09:24:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:24:21+00:00</t>
+    <t>2025-02-14T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:29:02+00:00</t>
+    <t>2025-02-14T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:34:15+00:00</t>
+    <t>2025-02-19T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T07:14:32+00:00</t>
+    <t>2025-02-19T08:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:04:21+00:00</t>
+    <t>2025-02-19T15:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:11:41+00:00</t>
+    <t>2025-02-19T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFLeistungskatalog-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:18:38+00:00</t>
+    <t>2025-02-19T15:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
